--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC679552-F58C-4A86-8789-63DEEABA3517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E758D6D5-A639-4CA0-A109-E0E07C853D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
@@ -79,12 +79,131 @@
         </r>
       </text>
     </comment>
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{9A1B8731-B991-4484-8CBE-32DE147DA1AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+La dirección es con 320, este inmueble esta con el numero 230
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{091407C6-C6B9-4D48-A516-FA0F0EE173FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">En la dirección es DA estaba separado, es decir, D A
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{4D4DCE3A-56D6-4DDB-899E-DF2F415CB8AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección el DA estaba separado, es decir, D A</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{3688AAC9-4700-4AA2-8FCF-9B368F29DBEF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+En la dirección es CR Y decia CL, tambien es DA estaba separado, es decir, D A</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
   <si>
     <t>Bloqueado</t>
   </si>
@@ -246,6 +365,175 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">15 DG 79 240 AP 304 URBANIZACION TORRES DE AVIÑON III PH                     </t>
+    </r>
+  </si>
+  <si>
+    <t>769-3737</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>TAMAYO BEDOYA LUZ DERLY DEL SOCORRO</t>
+  </si>
+  <si>
+    <t>32489257</t>
+  </si>
+  <si>
+    <t>SOTO CARDONA EDISON</t>
+  </si>
+  <si>
+    <t>1037582254</t>
+  </si>
+  <si>
+    <t>900575402</t>
+  </si>
+  <si>
+    <t>LOS CABOS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 75 DA 2 B SUR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>320</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> AP 235 CONJUNTO RESIDENCIAL LOS CABOS PH</t>
+    </r>
+  </si>
+  <si>
+    <t>679-4056</t>
+  </si>
+  <si>
+    <t>ARDILA VARGAS RODRIGO DE JESUS</t>
+  </si>
+  <si>
+    <t>71491531</t>
+  </si>
+  <si>
+    <t>MARIN MUÑOZ PAULA ANDREA</t>
+  </si>
+  <si>
+    <t>43983837</t>
+  </si>
+  <si>
+    <t>679-14895</t>
+  </si>
+  <si>
+    <t>BARRERA PALACIO CLAUDIA PATRICIA</t>
+  </si>
+  <si>
+    <t>43571158</t>
+  </si>
+  <si>
+    <t>GARCIA MONTAÑA ADRIANA YISELSS</t>
+  </si>
+  <si>
+    <t>53102229</t>
+  </si>
+  <si>
+    <t>EL LIBERTADOR LIM 12</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>DA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2 B SUR 320 AP 821 TO 6 CONJUNTO RESIDENCIAL LOS CABOS PH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>DA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2 B SUR 320 AP 828 LOS CABOS CONJUNTO RESIDENCIAL LOS CABOS PH</t>
+    </r>
+  </si>
+  <si>
+    <t>679-12747</t>
+  </si>
+  <si>
+    <t>VARGAS JULIO LIZET JOHANA</t>
+  </si>
+  <si>
+    <t>39321190</t>
+  </si>
+  <si>
+    <t>RESTREPO VALENCIA MARLENY DEL SOCORRO</t>
+  </si>
+  <si>
+    <t>42748695</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve"> CR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>DA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2 B SUR 320 AP 203 CONJUNTO RESIDENCIAL LOS CABOS P.H</t>
     </r>
   </si>
 </sst>
@@ -675,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1EC388-59EC-41A5-88B9-9B316DD532CA}">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -881,6 +1169,286 @@
       </c>
       <c r="W3" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3737</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10897</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1584300</v>
+      </c>
+      <c r="I4" s="3">
+        <v>271090</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1584300</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="2">
+        <v>7071155</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3983</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10447</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1727370</v>
+      </c>
+      <c r="I5" s="3">
+        <v>291303</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1727370</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" s="2">
+        <v>7046908</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="71.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2">
+        <v>6520</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="2">
+        <v>13198</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="V6" s="2">
+        <v>10057443</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="71.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6149</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6149</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1746067</v>
+      </c>
+      <c r="I7" s="3">
+        <v>362643</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1746067</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V7" s="2">
+        <v>6188118</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E758D6D5-A639-4CA0-A109-E0E07C853D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC64AD5-BD95-432F-AFEE-2FACBF6434FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC64AD5-BD95-432F-AFEE-2FACBF6434FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AC51BB-C368-4CC3-802E-807818E210BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AC51BB-C368-4CC3-802E-807818E210BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53427452-41BD-4EFD-803D-05CAD6B51E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
@@ -198,12 +198,541 @@
         </r>
       </text>
     </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{7910E56D-5010-4B3D-839F-E36F50413AAA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{2C628BDE-5B51-4D09-86CE-B06B66F37A0A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{ABDECD0F-558F-4662-B05E-7B17090F02A1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{1926E9DA-42FF-47B5-9418-A95AE6D97235}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{03BD058D-5F19-4B66-B1CA-85611379A461}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{EF9B3570-5585-4C6F-83E3-9070EE74B367}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{2878BF5F-4169-4DD1-9D32-486CA201C110}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{6B786EBE-C2D0-4B19-A736-E8EA2D8EE5C1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{FF4D59C8-1F92-432E-8BB1-1C2F9BED03DD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{715CE02B-3481-46C7-AEA7-CB7223E56514}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{14BEFBD5-44F9-4A47-83C3-365E684E8F27}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{F438789C-A32A-47A4-B390-D835F4F7A641}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{5417C991-4C05-49A9-ABCF-A46A26080E7E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{7EEAF900-477C-43E8-A643-6A2D783101FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En la dirección le falta la A luego del 43, según google maps es 43</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{AD280454-DFB5-4E1B-BC5C-09377309EA24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Le hace falta el </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>UR</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> a SUR, solo aparece la S y asi esta mal la dirección</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="186">
   <si>
     <t>Bloqueado</t>
   </si>
@@ -392,11 +921,300 @@
     <t>LOS CABOS</t>
   </si>
   <si>
+    <t>679-4056</t>
+  </si>
+  <si>
+    <t>ARDILA VARGAS RODRIGO DE JESUS</t>
+  </si>
+  <si>
+    <t>71491531</t>
+  </si>
+  <si>
+    <t>MARIN MUÑOZ PAULA ANDREA</t>
+  </si>
+  <si>
+    <t>43983837</t>
+  </si>
+  <si>
+    <t>679-14895</t>
+  </si>
+  <si>
+    <t>BARRERA PALACIO CLAUDIA PATRICIA</t>
+  </si>
+  <si>
+    <t>43571158</t>
+  </si>
+  <si>
+    <t>GARCIA MONTAÑA ADRIANA YISELSS</t>
+  </si>
+  <si>
+    <t>53102229</t>
+  </si>
+  <si>
+    <t>EL LIBERTADOR LIM 12</t>
+  </si>
+  <si>
+    <t>679-12747</t>
+  </si>
+  <si>
+    <t>VARGAS JULIO LIZET JOHANA</t>
+  </si>
+  <si>
+    <t>39321190</t>
+  </si>
+  <si>
+    <t>RESTREPO VALENCIA MARLENY DEL SOCORRO</t>
+  </si>
+  <si>
+    <t>42748695</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44918                                         </t>
+  </si>
+  <si>
+    <t>OSSA ZULUAGA FABIAN EUGENIO</t>
+  </si>
+  <si>
+    <t>71694858</t>
+  </si>
+  <si>
+    <t>DAZA GONZALEZ JUAN BAUTISTA</t>
+  </si>
+  <si>
+    <t>5164398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44799                                         </t>
+  </si>
+  <si>
+    <t>GOMEZ CARDEÑO DAVID</t>
+  </si>
+  <si>
+    <t>1152436144</t>
+  </si>
+  <si>
+    <t>FANO ESPINOSA JOHAN JAVIER</t>
+  </si>
+  <si>
+    <t>355576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44914                                         </t>
+  </si>
+  <si>
+    <t>SANCHEZ GOMEZ MATEO</t>
+  </si>
+  <si>
+    <t>1037655051</t>
+  </si>
+  <si>
+    <t>ESCOBAR GUTIERREZ LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>1216730356</t>
+  </si>
+  <si>
+    <t>SIN SEGURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45084                                         </t>
+  </si>
+  <si>
+    <t>GALVES PINEDA MARIA EUGENIA</t>
+  </si>
+  <si>
+    <t>43099023</t>
+  </si>
+  <si>
+    <t>CERON ESPINOSA OSCAR DAVID</t>
+  </si>
+  <si>
+    <t>1061764150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45128                                         </t>
+  </si>
+  <si>
+    <t>LAVERDE RESTREPO SANDRA MARIA</t>
+  </si>
+  <si>
+    <t>39443410</t>
+  </si>
+  <si>
+    <t>SOSA GIRALDO JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>71596355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44796                                         </t>
+  </si>
+  <si>
+    <t>BAENA PARRA ALMA NORA</t>
+  </si>
+  <si>
+    <t>21499251</t>
+  </si>
+  <si>
+    <t>RESTREPO JARAMILLO JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>1152706135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45390                                         </t>
+  </si>
+  <si>
+    <t>GRISALES GARZON JUAN DAVID</t>
+  </si>
+  <si>
+    <t>1032400834</t>
+  </si>
+  <si>
+    <t>LOPEZ CORREA CRISTINA</t>
+  </si>
+  <si>
+    <t>1037546405</t>
+  </si>
+  <si>
+    <t>901616972</t>
+  </si>
+  <si>
+    <t>CONJUNTO RESIDENCIAL METROPOLITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45516                                         </t>
+  </si>
+  <si>
+    <t>ARTEAGA FRANCO JAIRO CESAR</t>
+  </si>
+  <si>
+    <t>71669492</t>
+  </si>
+  <si>
+    <t>LOPEZ GIRALDO FAHUNDER GUILLERMO</t>
+  </si>
+  <si>
+    <t>1077866683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45789                                         </t>
+  </si>
+  <si>
+    <t>ZAPATA PATIÑO LINA MARIA</t>
+  </si>
+  <si>
+    <t>21527776</t>
+  </si>
+  <si>
+    <t>PEREZ BUILES SIMON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1152221893 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45096                                         </t>
+  </si>
+  <si>
+    <t>INVERSIONES LARES BERNAL SIERRA S A S</t>
+  </si>
+  <si>
+    <t>900178418</t>
+  </si>
+  <si>
+    <t>RESTREPO RESTREPO CARLOS ENRIQUE</t>
+  </si>
+  <si>
+    <t>15274289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45586                                         </t>
+  </si>
+  <si>
+    <t>ALZATE GOMEZ BLANCA DORIS</t>
+  </si>
+  <si>
+    <t>21462164</t>
+  </si>
+  <si>
+    <t>INCALL SAS</t>
+  </si>
+  <si>
+    <t>900753356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-46004                                         </t>
+  </si>
+  <si>
+    <t>GAVIRIA CALLE JUAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>98671798</t>
+  </si>
+  <si>
+    <t>WATERS JEREMIAH MICHAEL</t>
+  </si>
+  <si>
+    <t>1103739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45873                                         </t>
+  </si>
+  <si>
+    <t>ESTRADA ESCOBAR FELIPE</t>
+  </si>
+  <si>
+    <t>3413762</t>
+  </si>
+  <si>
+    <t>PINTO LOPEZ MANUEL CAMILO</t>
+  </si>
+  <si>
+    <t>1107078785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-46199                                         </t>
+  </si>
+  <si>
+    <t>INVERSIONES LARES BERNAL SIERRA SAS</t>
+  </si>
+  <si>
+    <t>MONTOYA OSORIO ADRIANA MARIA</t>
+  </si>
+  <si>
+    <t>42765551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44070                                         </t>
+  </si>
+  <si>
+    <t>AGUDELO MEJIA ROSALBA DE JESUS</t>
+  </si>
+  <si>
+    <t>43684294</t>
+  </si>
+  <si>
+    <t>SMARTALKING SAS</t>
+  </si>
+  <si>
+    <t>901381223</t>
+  </si>
+  <si>
+    <t>901112433</t>
+  </si>
+  <si>
+    <t>CONJUNTO RESIDENCIAL CITARK TORRES PH</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">CR 75 DA 2 B SUR </t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="MS Sans Serif"/>
@@ -413,44 +1231,12 @@
     </r>
   </si>
   <si>
-    <t>679-4056</t>
-  </si>
-  <si>
-    <t>ARDILA VARGAS RODRIGO DE JESUS</t>
-  </si>
-  <si>
-    <t>71491531</t>
-  </si>
-  <si>
-    <t>MARIN MUÑOZ PAULA ANDREA</t>
-  </si>
-  <si>
-    <t>43983837</t>
-  </si>
-  <si>
-    <t>679-14895</t>
-  </si>
-  <si>
-    <t>BARRERA PALACIO CLAUDIA PATRICIA</t>
-  </si>
-  <si>
-    <t>43571158</t>
-  </si>
-  <si>
-    <t>GARCIA MONTAÑA ADRIANA YISELSS</t>
-  </si>
-  <si>
-    <t>53102229</t>
-  </si>
-  <si>
-    <t>EL LIBERTADOR LIM 12</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">CR 75 </t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="MS Sans Serif"/>
@@ -472,6 +1258,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="MS Sans Serif"/>
@@ -488,28 +1275,30 @@
     </r>
   </si>
   <si>
-    <t>679-12747</t>
-  </si>
-  <si>
-    <t>VARGAS JULIO LIZET JOHANA</t>
-  </si>
-  <si>
-    <t>39321190</t>
-  </si>
-  <si>
-    <t>RESTREPO VALENCIA MARLENY DEL SOCORRO</t>
-  </si>
-  <si>
-    <t>42748695</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="MS Sans Serif"/>
       </rPr>
-      <t xml:space="preserve"> CR </t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>CR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -521,6 +1310,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="MS Sans Serif"/>
@@ -535,6 +1325,417 @@
       </rPr>
       <t xml:space="preserve"> 2 B SUR 320 AP 203 CONJUNTO RESIDENCIAL LOS CABOS P.H</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>CR 43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve">32 39  AP 1323 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN                   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1726 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN                      </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1921 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1924 CONJ  RESIDENCIAL METROPOLITAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 2024 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN                     </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1026 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1230 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 2132 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN                      </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1536 TO 1 CONJUNTO DE USO MIXTO METROPOLITAN PH              </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1830 CONJUNTO RESIDENCIAL METROPOLITAN              </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 726 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN TORRE 1               </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1435 TO 1 CONJUNTO RESIDENCIAL METROPOLITAN                      </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CR 43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 2023 TO 1 CONJUNTO DE USO MIXTO METROPOLITAN PH                  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CR 43 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39  AP 1821 TO 1 CONJUNTO DE USO MIXTO METROPOLITAN PH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CL 5 S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>UR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 25 233 AP 609 CONJUNTO RESIDENCIAL TORRES DE CITARK  P.H                 </t>
+    </r>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-41469 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV 38  AA 57 110 AP 1901 CONJUNTO RESIDENCIAL PUERTO PARAISO PH   </t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>ARANGO PARDO RICARDO</t>
+  </si>
+  <si>
+    <t>1020408447</t>
+  </si>
+  <si>
+    <t>HENAO VILLADA DEISY FERNANDA</t>
+  </si>
+  <si>
+    <t>1017269223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-44741                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV 38 AA 57 110 523 CONJUNTO RESIDENCIAL PUERTO PARAISO PH </t>
+  </si>
+  <si>
+    <t>HERRERA GOMEZ JUAN PABLO</t>
+  </si>
+  <si>
+    <t>1037592253</t>
+  </si>
+  <si>
+    <t>VALLEJO SANCHEZ LEISSA YULIETH</t>
+  </si>
+  <si>
+    <t>1152211342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45617                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV 38 AA  57 110 AP 1215 CONJUNTO RESIDENCIAL PUERTO PARAISO PH          </t>
+  </si>
+  <si>
+    <t>OCHOA ARAUJO LILIANA MARGARITA</t>
+  </si>
+  <si>
+    <t>23217400</t>
+  </si>
+  <si>
+    <t>OCHOA MENDOZA OSCAR ANDRES</t>
+  </si>
+  <si>
+    <t>1016094982</t>
+  </si>
+  <si>
+    <t>901453434</t>
+  </si>
+  <si>
+    <t>CONJUNTO RESIDENCIAL PUERTO PARAISO PH</t>
   </si>
 </sst>
 </file>
@@ -963,7 +2164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1EC388-59EC-41A5-88B9-9B316DD532CA}">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -1188,7 +2389,7 @@
         <v>10897</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>26</v>
@@ -1253,13 +2454,13 @@
         <v>3983</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2">
         <v>10447</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
@@ -1283,19 +2484,19 @@
         <v>23</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>47</v>
@@ -1324,13 +2525,13 @@
         <v>6520</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2">
         <v>13198</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>26</v>
@@ -1354,24 +2555,24 @@
         <v>23</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V6" s="2">
         <v>10057443</v>
@@ -1391,13 +2592,13 @@
         <v>6149</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2">
         <v>6149</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>26</v>
@@ -1421,19 +2622,19 @@
         <v>23</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>47</v>
@@ -1449,6 +2650,1224 @@
       </c>
       <c r="W7" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2">
+        <v>14367</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="2">
+        <v>14367</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V8" s="2">
+        <v>7501138</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2">
+        <v>14368</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="2">
+        <v>14368</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2950000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2950000</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V9" s="2">
+        <v>10170493</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="2">
+        <v>14389</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2">
+        <v>14389</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V10" s="2">
+        <v>10175765</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="51" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2">
+        <v>14468</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="2">
+        <v>14468</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V11" s="2">
+        <v>7512028</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2">
+        <v>14559</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="2">
+        <v>14559</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V12" s="2">
+        <v>10189755</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2">
+        <v>14597</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="2">
+        <v>14597</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V13" s="2">
+        <v>10196872</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2">
+        <v>14608</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="2">
+        <v>14608</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>172270</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V14" s="2">
+        <v>7519243</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14658</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="2">
+        <v>14658</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3200000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3200000</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V15" s="2">
+        <v>10207339</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2">
+        <v>14779</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="2">
+        <v>14779</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V16" s="2">
+        <v>10217961</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2">
+        <v>14808</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="2">
+        <v>14808</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3100000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3100000</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V17" s="2">
+        <v>10224134</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="2">
+        <v>14877</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="2">
+        <v>14877</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V18" s="2">
+        <v>10231192</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="2">
+        <v>14942</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="2">
+        <v>14942</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="3">
+        <v>3100000</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>3100000</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V19" s="2">
+        <v>7530923</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="2">
+        <v>14974</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="2">
+        <v>14974</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V20" s="2">
+        <v>10220686</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="2">
+        <v>14999</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="2">
+        <v>14999</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2700000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>2700000</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V21" s="2">
+        <v>7508669</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="2">
+        <v>14046</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="2">
+        <v>14046</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5615000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>600486</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5615000</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V22" s="2">
+        <v>10137891</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="2">
+        <v>12960</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="2">
+        <v>12960</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V23" s="2">
+        <v>10035390</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="2">
+        <v>14292</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="2">
+        <v>14292</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V24" s="2">
+        <v>7504739</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="2">
+        <v>14720</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="2">
+        <v>14720</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>129751</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V25" s="2">
+        <v>10214467</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53427452-41BD-4EFD-803D-05CAD6B51E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE9831A-BCBD-418A-9F3B-1154A54CE59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
@@ -727,6 +727,79 @@
         </r>
       </text>
     </comment>
+    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{3DBA0C4A-5D2E-42B5-9FF0-D86CF2EA4CF5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Entre el # 38 y la AA habia dos espacios y no encaja con la dirección del mismo conjunto
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{A74E7583-EEA4-4C7C-B3A9-B888FBD310D1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Le falta el AP al número del apartamento </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{C022512F-397A-4F89-9209-70C4F3E505AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Entre la AA y el # 57 habia dos espacios y no encaja con la dirección del mismo conjunto</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1678,9 +1751,6 @@
     <t xml:space="preserve">679-41469 </t>
   </si>
   <si>
-    <t xml:space="preserve">TV 38  AA 57 110 AP 1901 CONJUNTO RESIDENCIAL PUERTO PARAISO PH   </t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
@@ -1699,9 +1769,6 @@
     <t xml:space="preserve">679-44741                                         </t>
   </si>
   <si>
-    <t xml:space="preserve">TV 38 AA 57 110 523 CONJUNTO RESIDENCIAL PUERTO PARAISO PH </t>
-  </si>
-  <si>
     <t>HERRERA GOMEZ JUAN PABLO</t>
   </si>
   <si>
@@ -1717,9 +1784,6 @@
     <t xml:space="preserve">679-45617                                         </t>
   </si>
   <si>
-    <t xml:space="preserve">TV 38 AA  57 110 AP 1215 CONJUNTO RESIDENCIAL PUERTO PARAISO PH          </t>
-  </si>
-  <si>
     <t>OCHOA ARAUJO LILIANA MARGARITA</t>
   </si>
   <si>
@@ -1736,6 +1800,34 @@
   </si>
   <si>
     <t>CONJUNTO RESIDENCIAL PUERTO PARAISO PH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV 38 AA 57 110 AP 1901 CONJUNTO RESIDENCIAL PUERTO PARAISO PH   </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TV 38 AA 57 110 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t xml:space="preserve">AP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">523 CONJUNTO RESIDENCIAL PUERTO PARAISO PH </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TV 38 AA 57 110 AP 1215 CONJUNTO RESIDENCIAL PUERTO PARAISO PH          </t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1837,7 @@
   <numFmts count="1">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;\ #,##0.00;\-&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1790,6 +1882,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3682,10 +3781,10 @@
         <v>12960</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="H23" s="3">
         <v>1250000</v>
@@ -3706,19 +3805,19 @@
         <v>23</v>
       </c>
       <c r="N23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -3743,16 +3842,16 @@
         <v>14292</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E24" s="2">
         <v>14292</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H24" s="3">
         <v>1250000</v>
@@ -3773,19 +3872,19 @@
         <v>23</v>
       </c>
       <c r="N24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -3810,16 +3909,16 @@
         <v>14720</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2">
         <v>14720</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3">
         <v>1400000</v>
@@ -3840,25 +3939,25 @@
         <v>23</v>
       </c>
       <c r="N25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="U25" s="1" t="s">
         <v>81</v>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE9831A-BCBD-418A-9F3B-1154A54CE59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B6B8A9-8811-462B-BD43-2F67099CAE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B6B8A9-8811-462B-BD43-2F67099CAE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FEC985-F8CC-4EB8-AC73-16E6DEAED71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
@@ -800,12 +800,156 @@
         </r>
       </text>
     </comment>
+    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{C0086625-13D1-4E6E-BFF6-B9A1FE5274CB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="0" shapeId="0" xr:uid="{43F805F4-D06D-4F6D-927F-7BA9F8A656DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{C73BC160-A739-4F2C-8C3A-391C2454AC41}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{B0F31F5F-1BAB-478B-A220-781541224DBD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0" shapeId="0" xr:uid="{BBE63E79-CA9F-4377-8797-C40F4074DF7E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{EC09E741-958F-4F17-9CD2-3B188CC75B6A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>En vez de decir TV decia TRAN, lo cual dificulta la leida de los datos, el diminutivo es TV</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="226">
   <si>
     <t>Bloqueado</t>
   </si>
@@ -1827,7 +1971,239 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TV 38 AA 57 110 AP 1215 CONJUNTO RESIDENCIAL PUERTO PARAISO PH          </t>
+    <t xml:space="preserve">679-45161                                         </t>
+  </si>
+  <si>
+    <t>ELORZA PEREZ LAURA MELISSA</t>
+  </si>
+  <si>
+    <t>1017220272</t>
+  </si>
+  <si>
+    <t>ZAPATA GIRALDO DANILO</t>
+  </si>
+  <si>
+    <t>6706835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45642                                         </t>
+  </si>
+  <si>
+    <t>ACOSTA CANO OMAIRA</t>
+  </si>
+  <si>
+    <t>42820044</t>
+  </si>
+  <si>
+    <t>VILLA PALACIO ELIZABETH</t>
+  </si>
+  <si>
+    <t>1128266253</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-45921                                         </t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>URREA ARISTIZABAL JOSE IVAN</t>
+  </si>
+  <si>
+    <t>70826092</t>
+  </si>
+  <si>
+    <t>PRADA BARROS GRACE DEL CARMEN</t>
+  </si>
+  <si>
+    <t>22377796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-46143                                         </t>
+  </si>
+  <si>
+    <t>GOMEZ JARAMILLO MARIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>42888423</t>
+  </si>
+  <si>
+    <t>ZULUAGA RAMIREZ VIVIANA MARCELA</t>
+  </si>
+  <si>
+    <t>43996788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-46218                                         </t>
+  </si>
+  <si>
+    <t>GIRALDO CATAÑO MARY LUZ</t>
+  </si>
+  <si>
+    <t>43816342</t>
+  </si>
+  <si>
+    <t>GIL ZAPATA LINA MARIA</t>
+  </si>
+  <si>
+    <t>43108182</t>
+  </si>
+  <si>
+    <t>901128927</t>
+  </si>
+  <si>
+    <t>URBANIZACIÓN PUERTO ALEGRE PH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679-46684                                         </t>
+  </si>
+  <si>
+    <t>VALENCIA ESCOBAR FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>71748896</t>
+  </si>
+  <si>
+    <t>GIRALDO MUÑOZ JUAN JOSE</t>
+  </si>
+  <si>
+    <t>1020482241</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">  38 AA  57 110 AP 1422 CONJ RESIDENCIAL PUERTO PARAÍSO PH                  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 38 AA 57 110 AP 1215 CONJUNTO RESIDENCIAL PUERTO PARAISO PH          </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 15 DG 79 240 AP 501 URBANIZACION TORRES DE AVIÑON III                      </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 33 B SUR 39 21                     </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 15 DG 79 120 INT 309 EDIFICIOS TORRES DE AVIÑON 1 Y 2 PH </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 38 AA 59 A 231 AP 1829 URBANIZACION PUERTO ALEGRE PH                       </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Sans Serif"/>
+      </rPr>
+      <t>TV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="MS Sans Serif"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 38 AA 57 110 AP 2214 CONJUNTO RESIDENCIAL PUERTO PARAISO PH                </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2263,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1EC388-59EC-41A5-88B9-9B316DD532CA}">
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -3914,8 +4290,8 @@
       <c r="E25" s="2">
         <v>14720</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>185</v>
+      <c r="F25" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>166</v>
@@ -3967,6 +4343,416 @@
       </c>
       <c r="W25" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="2">
+        <v>14534</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="2">
+        <v>14534</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>129751</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V26" s="2">
+        <v>10197133</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="51" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2">
+        <v>14704</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="2">
+        <v>14704</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V27" s="2">
+        <v>7522142</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="2">
+        <v>14835</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="2">
+        <v>14835</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V28" s="2">
+        <v>7526293</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="2">
+        <v>14948</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" s="2">
+        <v>14948</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V29" s="2">
+        <v>10237992</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="51" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="2">
+        <v>14982</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="2">
+        <v>14982</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="I30" s="3">
+        <v>135904</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V30" s="2">
+        <v>10243407</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="2">
+        <v>15168</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="2">
+        <v>15168</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1400000</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V31" s="2">
+        <v>10263814</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FEC985-F8CC-4EB8-AC73-16E6DEAED71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5A89C7-6E76-4167-836C-6E32D2CC50E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8964" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/data/Direcciones_corr.xlsx
+++ b/data/Direcciones_corr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\PortadaInmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5A89C7-6E76-4167-836C-6E32D2CC50E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481772B1-C343-40B2-8F18-96C1B42C478A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8964" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8964" xr2:uid="{D30C8B63-D13B-4568-A666-E79AB393F095}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2277,6 +2277,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2308,7 +2314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2323,6 +2329,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2729,7 +2741,7 @@
       <c r="E2" s="2">
         <v>10905</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -2796,7 +2808,7 @@
       <c r="E3" s="2">
         <v>10659</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -4223,7 +4235,7 @@
       <c r="E24" s="2">
         <v>14292</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="7" t="s">
         <v>184</v>
       </c>
       <c r="G24" s="1" t="s">
